--- a/evaluation/evaluation_bertscore_table.xlsx
+++ b/evaluation/evaluation_bertscore_table.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="54">
   <si>
     <t>No</t>
   </si>
@@ -31,148 +31,151 @@
     <t>SEMANTIC_SIMILARITY</t>
   </si>
   <si>
-    <t>Rerata</t>
-  </si>
-  <si>
-    <t>87.57%</t>
-  </si>
-  <si>
-    <t>87.80%</t>
-  </si>
-  <si>
-    <t>70.13%</t>
-  </si>
-  <si>
-    <t>90.17%</t>
-  </si>
-  <si>
-    <t>89.13%</t>
-  </si>
-  <si>
-    <t>61.87%</t>
-  </si>
-  <si>
-    <t>94.56%</t>
-  </si>
-  <si>
-    <t>94.47%</t>
-  </si>
-  <si>
-    <t>83.77%</t>
-  </si>
-  <si>
-    <t>77.89%</t>
-  </si>
-  <si>
-    <t>95.27%</t>
-  </si>
-  <si>
-    <t>82.71%</t>
-  </si>
-  <si>
-    <t>80.30%</t>
-  </si>
-  <si>
-    <t>97.50%</t>
-  </si>
-  <si>
-    <t>67.53%</t>
-  </si>
-  <si>
-    <t>84.05%</t>
-  </si>
-  <si>
-    <t>91.94%</t>
-  </si>
-  <si>
-    <t>92.03%</t>
-  </si>
-  <si>
-    <t>69.34%</t>
-  </si>
-  <si>
-    <t>94.73%</t>
-  </si>
-  <si>
-    <t>90.04%</t>
-  </si>
-  <si>
-    <t>60.12%</t>
-  </si>
-  <si>
-    <t>87.79%</t>
-  </si>
-  <si>
-    <t>86.98%</t>
-  </si>
-  <si>
-    <t>95.62%</t>
-  </si>
-  <si>
-    <t>78.61%</t>
-  </si>
-  <si>
-    <t>95.26%</t>
-  </si>
-  <si>
-    <t>90.98%</t>
-  </si>
-  <si>
-    <t>88.32%</t>
-  </si>
-  <si>
-    <t>89.49%</t>
-  </si>
-  <si>
-    <t>71.40%</t>
-  </si>
-  <si>
-    <t>85.51%</t>
-  </si>
-  <si>
-    <t>89.70%</t>
-  </si>
-  <si>
-    <t>89.87%</t>
-  </si>
-  <si>
-    <t>69.73%</t>
-  </si>
-  <si>
-    <t>92.39%</t>
-  </si>
-  <si>
-    <t>89.59%</t>
-  </si>
-  <si>
-    <t>60.98%</t>
-  </si>
-  <si>
-    <t>91.05%</t>
+    <t>Rata-rata</t>
+  </si>
+  <si>
+    <t>80.28%</t>
+  </si>
+  <si>
+    <t>92.10%</t>
+  </si>
+  <si>
+    <t>47.84%</t>
+  </si>
+  <si>
+    <t>89.30%</t>
+  </si>
+  <si>
+    <t>89.06%</t>
+  </si>
+  <si>
+    <t>49.98%</t>
+  </si>
+  <si>
+    <t>88.99%</t>
+  </si>
+  <si>
+    <t>85.23%</t>
+  </si>
+  <si>
+    <t>67.46%</t>
+  </si>
+  <si>
+    <t>75.90%</t>
+  </si>
+  <si>
+    <t>93.74%</t>
+  </si>
+  <si>
+    <t>81.63%</t>
+  </si>
+  <si>
+    <t>75.00%</t>
+  </si>
+  <si>
+    <t>44.65%</t>
+  </si>
+  <si>
+    <t>51.92%</t>
+  </si>
+  <si>
+    <t>74.20%</t>
+  </si>
+  <si>
+    <t>81.14%</t>
+  </si>
+  <si>
+    <t>94.70%</t>
+  </si>
+  <si>
+    <t>55.01%</t>
+  </si>
+  <si>
+    <t>94.19%</t>
   </si>
   <si>
     <t>90.57%</t>
   </si>
   <si>
-    <t>89.31%</t>
-  </si>
-  <si>
-    <t>78.25%</t>
-  </si>
-  <si>
-    <t>86.65%</t>
-  </si>
-  <si>
-    <t>84.12%</t>
-  </si>
-  <si>
-    <t>93.32%</t>
-  </si>
-  <si>
-    <t>69.41%</t>
-  </si>
-  <si>
-    <t>84.68%</t>
+    <t>57.38%</t>
+  </si>
+  <si>
+    <t>82.37%</t>
+  </si>
+  <si>
+    <t>80.63%</t>
+  </si>
+  <si>
+    <t>64.01%</t>
+  </si>
+  <si>
+    <t>67.36%</t>
+  </si>
+  <si>
+    <t>91.21%</t>
+  </si>
+  <si>
+    <t>90.31%</t>
+  </si>
+  <si>
+    <t>74.51%</t>
+  </si>
+  <si>
+    <t>56.22%</t>
+  </si>
+  <si>
+    <t>56.97%</t>
+  </si>
+  <si>
+    <t>75.77%</t>
+  </si>
+  <si>
+    <t>80.71%</t>
+  </si>
+  <si>
+    <t>93.38%</t>
+  </si>
+  <si>
+    <t>51.18%</t>
+  </si>
+  <si>
+    <t>91.68%</t>
+  </si>
+  <si>
+    <t>89.81%</t>
+  </si>
+  <si>
+    <t>53.43%</t>
+  </si>
+  <si>
+    <t>85.55%</t>
+  </si>
+  <si>
+    <t>82.86%</t>
+  </si>
+  <si>
+    <t>65.69%</t>
+  </si>
+  <si>
+    <t>71.37%</t>
+  </si>
+  <si>
+    <t>92.46%</t>
+  </si>
+  <si>
+    <t>85.75%</t>
+  </si>
+  <si>
+    <t>74.75%</t>
+  </si>
+  <si>
+    <t>49.77%</t>
+  </si>
+  <si>
+    <t>54.33%</t>
+  </si>
+  <si>
+    <t>74.85%</t>
   </si>
 </sst>
 </file>
@@ -731,10 +734,10 @@
         <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -748,10 +751,10 @@
         <v>33</v>
       </c>
       <c r="D13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -765,10 +768,10 @@
         <v>34</v>
       </c>
       <c r="D14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -782,10 +785,10 @@
         <v>35</v>
       </c>
       <c r="D15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -799,10 +802,10 @@
         <v>36</v>
       </c>
       <c r="D16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -816,10 +819,10 @@
         <v>37</v>
       </c>
       <c r="D17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
